--- a/ssp_modeling/transformations/templates/calibrated/libya/model_input_variables_libya_se_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/libya/model_input_variables_libya_se_calibrated.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="strategy_id-0" sheetId="1" r:id="rId1"/>
-    <sheet name="strategy_id-6002" sheetId="2" r:id="rId2"/>
+    <sheet name="strategy_id-6000" sheetId="2" r:id="rId2"/>
+    <sheet name="strategy_id-6002" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="22">
   <si>
     <t>subsector</t>
   </si>
@@ -2198,4 +2199,276 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AS2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2</v>
+      </c>
+      <c r="M1" s="1">
+        <v>3</v>
+      </c>
+      <c r="N1" s="1">
+        <v>4</v>
+      </c>
+      <c r="O1" s="1">
+        <v>5</v>
+      </c>
+      <c r="P1" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>7</v>
+      </c>
+      <c r="R1" s="1">
+        <v>8</v>
+      </c>
+      <c r="S1" s="1">
+        <v>9</v>
+      </c>
+      <c r="T1" s="1">
+        <v>10</v>
+      </c>
+      <c r="U1" s="1">
+        <v>11</v>
+      </c>
+      <c r="V1" s="1">
+        <v>12</v>
+      </c>
+      <c r="W1" s="1">
+        <v>13</v>
+      </c>
+      <c r="X1" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>16</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>17</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>18</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>19</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>20</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>21</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>22</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>23</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>24</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>25</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>26</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>27</v>
+      </c>
+      <c r="AL1" s="1">
+        <v>28</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>29</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>30</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>32</v>
+      </c>
+      <c r="AQ1" s="1">
+        <v>33</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>34</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>13</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0.99</v>
+      </c>
+      <c r="L2">
+        <v>0.98</v>
+      </c>
+      <c r="M2">
+        <v>0.97</v>
+      </c>
+      <c r="N2">
+        <v>0.96</v>
+      </c>
+      <c r="O2">
+        <v>0.95</v>
+      </c>
+      <c r="P2">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>0.93</v>
+      </c>
+      <c r="R2">
+        <v>0.92</v>
+      </c>
+      <c r="S2">
+        <v>0.91</v>
+      </c>
+      <c r="T2">
+        <v>0.9</v>
+      </c>
+      <c r="U2">
+        <v>0.89</v>
+      </c>
+      <c r="V2">
+        <v>0.88</v>
+      </c>
+      <c r="W2">
+        <v>0.8539130434782609</v>
+      </c>
+      <c r="X2">
+        <v>0.8286956521739131</v>
+      </c>
+      <c r="Y2">
+        <v>0.8043478260869564</v>
+      </c>
+      <c r="Z2">
+        <v>0.7808695652173914</v>
+      </c>
+      <c r="AA2">
+        <v>0.7582608695652174</v>
+      </c>
+      <c r="AB2">
+        <v>0.7365217391304347</v>
+      </c>
+      <c r="AC2">
+        <v>0.7156521739130435</v>
+      </c>
+      <c r="AD2">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="AE2">
+        <v>0.6765217391304349</v>
+      </c>
+      <c r="AF2">
+        <v>0.6582608695652175</v>
+      </c>
+      <c r="AG2">
+        <v>0.6408695652173912</v>
+      </c>
+      <c r="AH2">
+        <v>0.6243478260869566</v>
+      </c>
+      <c r="AI2">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="AJ2">
+        <v>0.5939130434782609</v>
+      </c>
+      <c r="AK2">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AL2">
+        <v>0.5669565217391305</v>
+      </c>
+      <c r="AM2">
+        <v>0.5547826086956522</v>
+      </c>
+      <c r="AN2">
+        <v>0.5434782608695652</v>
+      </c>
+      <c r="AO2">
+        <v>0.5347826086956522</v>
+      </c>
+      <c r="AP2">
+        <v>0.5260869565217391</v>
+      </c>
+      <c r="AQ2">
+        <v>0.5173913043478261</v>
+      </c>
+      <c r="AR2">
+        <v>0.508695652173913</v>
+      </c>
+      <c r="AS2">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>